--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5fdc4b1627766374</t>
+          <t>5cdd42e09dfe5d95</t>
         </is>
       </c>
     </row>

--- a/companies/lgd/model.xlsx
+++ b/companies/lgd/model.xlsx
@@ -4823,7 +4823,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5cdd42e09dfe5d95</t>
+          <t>2a3da87c288d67de</t>
         </is>
       </c>
     </row>
